--- a/Book2.xlsx
+++ b/Book2.xlsx
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MITS\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1FC4FAF6-62D5-4C8B-880A-5D9C71CCB1D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E98F224-20B5-429A-A015-AE254CE1964B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9BACECEB-375B-42C4-A1A1-1837808C4DD3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{9BACECEB-375B-42C4-A1A1-1837808C4DD3}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet5" sheetId="5" r:id="rId1"/>
+    <sheet name="Sheet6" sheetId="6" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId4"/>
+    <externalReference r:id="rId5"/>
+  </externalReferences>
   <definedNames>
     <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$I$2:$I$30</definedName>
     <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$N$2:$N$30</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$I$3:$I$31</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Sheet1!$N$3:$N$31</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">Sheet1!$I$3:$I$31</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">Sheet1!$N$3:$N$31</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">Sheet1!$I$2:$I$30</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">Sheet1!$N$2:$N$30</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -102,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="120">
   <si>
     <t>customerID</t>
   </si>
@@ -286,6 +286,183 @@
   <si>
     <t>Zeros</t>
   </si>
+  <si>
+    <t>Column 1</t>
+  </si>
+  <si>
+    <t>Column 2</t>
+  </si>
+  <si>
+    <t>Column1</t>
+  </si>
+  <si>
+    <t>Column2</t>
+  </si>
+  <si>
+    <t>Mean</t>
+  </si>
+  <si>
+    <t>Standard Error</t>
+  </si>
+  <si>
+    <t>Median</t>
+  </si>
+  <si>
+    <t>Mode</t>
+  </si>
+  <si>
+    <t>Standard Deviation</t>
+  </si>
+  <si>
+    <t>Sample Variance</t>
+  </si>
+  <si>
+    <t>Kurtosis</t>
+  </si>
+  <si>
+    <t>Skewness</t>
+  </si>
+  <si>
+    <t>Range</t>
+  </si>
+  <si>
+    <t>Minimum</t>
+  </si>
+  <si>
+    <t>Maximum</t>
+  </si>
+  <si>
+    <t>Sum</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Bin</t>
+  </si>
+  <si>
+    <t>Frequency</t>
+  </si>
+  <si>
+    <t>More</t>
+  </si>
+  <si>
+    <t>Anova: Single Factor</t>
+  </si>
+  <si>
+    <t>SUMMARY</t>
+  </si>
+  <si>
+    <t>Groups</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>Variance</t>
+  </si>
+  <si>
+    <t>ANOVA</t>
+  </si>
+  <si>
+    <t>Source of Variation</t>
+  </si>
+  <si>
+    <t>SS</t>
+  </si>
+  <si>
+    <t>df</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>P-value</t>
+  </si>
+  <si>
+    <t>F crit</t>
+  </si>
+  <si>
+    <t>Between Groups</t>
+  </si>
+  <si>
+    <t>Within Groups</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>bina</t>
+  </si>
+  <si>
+    <t>SUMMARY OUTPUT</t>
+  </si>
+  <si>
+    <t>Regression Statistics</t>
+  </si>
+  <si>
+    <t>Multiple R</t>
+  </si>
+  <si>
+    <t>R Square</t>
+  </si>
+  <si>
+    <t>Adjusted R Square</t>
+  </si>
+  <si>
+    <t>Observations</t>
+  </si>
+  <si>
+    <t>Regression</t>
+  </si>
+  <si>
+    <t>Residual</t>
+  </si>
+  <si>
+    <t>Intercept</t>
+  </si>
+  <si>
+    <t>Significance F</t>
+  </si>
+  <si>
+    <t>Coefficients</t>
+  </si>
+  <si>
+    <t>t Stat</t>
+  </si>
+  <si>
+    <t>Lower 95%</t>
+  </si>
+  <si>
+    <t>Upper 95%</t>
+  </si>
+  <si>
+    <t>Lower 95.0%</t>
+  </si>
+  <si>
+    <t>Upper 95.0%</t>
+  </si>
+  <si>
+    <t>X Variable 1</t>
+  </si>
+  <si>
+    <t>RESIDUAL OUTPUT</t>
+  </si>
+  <si>
+    <t>Observation</t>
+  </si>
+  <si>
+    <t>Predicted Y</t>
+  </si>
+  <si>
+    <t>Residuals</t>
+  </si>
+  <si>
+    <t>Standard Residuals</t>
+  </si>
 </sst>
 </file>
 
@@ -300,7 +477,7 @@
     <numFmt numFmtId="169" formatCode="#,##0;"/>
     <numFmt numFmtId="170" formatCode=";;#,##0;"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -334,6 +511,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -361,7 +546,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -445,11 +630,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -486,6 +691,18 @@
     <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="170" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1117,6 +1334,11 @@
               </a:effectLst>
               <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-6853-4C1A-A693-4C4B9BBC2693}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -1137,6 +1359,11 @@
               </a:effectLst>
               <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-6853-4C1A-A693-4C4B9BBC2693}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -1157,6 +1384,11 @@
               </a:effectLst>
               <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-6853-4C1A-A693-4C4B9BBC2693}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -1177,6 +1409,11 @@
               </a:effectLst>
               <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-6853-4C1A-A693-4C4B9BBC2693}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
@@ -1197,6 +1434,11 @@
               </a:effectLst>
               <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-6853-4C1A-A693-4C4B9BBC2693}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
@@ -1217,6 +1459,11 @@
               </a:effectLst>
               <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-6853-4C1A-A693-4C4B9BBC2693}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="6"/>
@@ -1239,6 +1486,11 @@
               </a:effectLst>
               <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000D-6853-4C1A-A693-4C4B9BBC2693}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="7"/>
@@ -1261,6 +1513,11 @@
               </a:effectLst>
               <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000F-6853-4C1A-A693-4C4B9BBC2693}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="8"/>
@@ -1283,6 +1540,11 @@
               </a:effectLst>
               <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000011-6853-4C1A-A693-4C4B9BBC2693}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="9"/>
@@ -1305,6 +1567,11 @@
               </a:effectLst>
               <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000013-6853-4C1A-A693-4C4B9BBC2693}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="10"/>
@@ -1327,6 +1594,11 @@
               </a:effectLst>
               <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000015-6853-4C1A-A693-4C4B9BBC2693}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="11"/>
@@ -1349,6 +1621,11 @@
               </a:effectLst>
               <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000017-6853-4C1A-A693-4C4B9BBC2693}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="12"/>
@@ -1372,6 +1649,11 @@
               </a:effectLst>
               <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000019-6853-4C1A-A693-4C4B9BBC2693}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="13"/>
@@ -1395,6 +1677,11 @@
               </a:effectLst>
               <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001B-6853-4C1A-A693-4C4B9BBC2693}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="14"/>
@@ -1418,6 +1705,11 @@
               </a:effectLst>
               <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001D-6853-4C1A-A693-4C4B9BBC2693}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="15"/>
@@ -1441,6 +1733,11 @@
               </a:effectLst>
               <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001F-6853-4C1A-A693-4C4B9BBC2693}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="16"/>
@@ -1464,6 +1761,11 @@
               </a:effectLst>
               <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000021-6853-4C1A-A693-4C4B9BBC2693}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="17"/>
@@ -1487,6 +1789,11 @@
               </a:effectLst>
               <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000023-6853-4C1A-A693-4C4B9BBC2693}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="18"/>
@@ -1509,6 +1816,11 @@
               </a:effectLst>
               <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000025-6853-4C1A-A693-4C4B9BBC2693}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="19"/>
@@ -1531,6 +1843,11 @@
               </a:effectLst>
               <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000027-6853-4C1A-A693-4C4B9BBC2693}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="20"/>
@@ -1553,6 +1870,11 @@
               </a:effectLst>
               <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000029-6853-4C1A-A693-4C4B9BBC2693}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="21"/>
@@ -1575,6 +1897,11 @@
               </a:effectLst>
               <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000002B-6853-4C1A-A693-4C4B9BBC2693}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="22"/>
@@ -1597,6 +1924,11 @@
               </a:effectLst>
               <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000002D-6853-4C1A-A693-4C4B9BBC2693}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="23"/>
@@ -1619,6 +1951,11 @@
               </a:effectLst>
               <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000002F-6853-4C1A-A693-4C4B9BBC2693}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="24"/>
@@ -1642,6 +1979,11 @@
               </a:effectLst>
               <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000031-6853-4C1A-A693-4C4B9BBC2693}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="25"/>
@@ -1665,6 +2007,11 @@
               </a:effectLst>
               <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000033-6853-4C1A-A693-4C4B9BBC2693}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="26"/>
@@ -1688,6 +2035,11 @@
               </a:effectLst>
               <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000035-6853-4C1A-A693-4C4B9BBC2693}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="27"/>
@@ -1711,6 +2063,11 @@
               </a:effectLst>
               <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000037-6853-4C1A-A693-4C4B9BBC2693}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="28"/>
@@ -1734,6 +2091,11 @@
               </a:effectLst>
               <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000039-6853-4C1A-A693-4C4B9BBC2693}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>
@@ -3221,88 +3583,88 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>510959</c:v>
+                  <c:v>568889</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>538145</c:v>
+                  <c:v>528570</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>568241</c:v>
+                  <c:v>542485</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>571948</c:v>
+                  <c:v>587693</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>564565</c:v>
+                  <c:v>534143</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>580122</c:v>
+                  <c:v>575339</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>516124</c:v>
+                  <c:v>525835</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>511225</c:v>
+                  <c:v>539920</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>569774</c:v>
+                  <c:v>516361</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>556456</c:v>
+                  <c:v>598341</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>581168</c:v>
+                  <c:v>524749</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>528846</c:v>
+                  <c:v>530291</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>549625</c:v>
+                  <c:v>515539</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>517350</c:v>
+                  <c:v>506837</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>574068</c:v>
+                  <c:v>568312</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>559107</c:v>
+                  <c:v>529702</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>573138</c:v>
+                  <c:v>500720</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>595209</c:v>
+                  <c:v>554194</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>580002</c:v>
+                  <c:v>509430</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>563644</c:v>
+                  <c:v>543981</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>511466</c:v>
+                  <c:v>545125</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>514463</c:v>
+                  <c:v>538621</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>527021</c:v>
+                  <c:v>515503</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>589750</c:v>
+                  <c:v>525936</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>584995</c:v>
+                  <c:v>553223</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>545258</c:v>
+                  <c:v>552509</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>503674</c:v>
+                  <c:v>522056</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>523767</c:v>
+                  <c:v>539927</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5114,6 +5476,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-0AF8-451B-A2B2-7BD22E246F6D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -5140,6 +5507,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-0AF8-451B-A2B2-7BD22E246F6D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -5166,6 +5538,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-0AF8-451B-A2B2-7BD22E246F6D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -5192,6 +5569,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-0AF8-451B-A2B2-7BD22E246F6D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
@@ -5218,6 +5600,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-0AF8-451B-A2B2-7BD22E246F6D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
@@ -5244,6 +5631,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-0AF8-451B-A2B2-7BD22E246F6D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="6"/>
@@ -5273,6 +5665,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000D-0AF8-451B-A2B2-7BD22E246F6D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="7"/>
@@ -5302,6 +5699,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000F-0AF8-451B-A2B2-7BD22E246F6D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="8"/>
@@ -5331,6 +5733,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000011-0AF8-451B-A2B2-7BD22E246F6D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="9"/>
@@ -5360,6 +5767,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000013-0AF8-451B-A2B2-7BD22E246F6D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="10"/>
@@ -5389,6 +5801,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000015-0AF8-451B-A2B2-7BD22E246F6D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="11"/>
@@ -5418,6 +5835,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000017-0AF8-451B-A2B2-7BD22E246F6D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="12"/>
@@ -5449,6 +5871,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000019-0AF8-451B-A2B2-7BD22E246F6D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="13"/>
@@ -5480,6 +5907,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001B-0AF8-451B-A2B2-7BD22E246F6D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="14"/>
@@ -5511,6 +5943,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001D-0AF8-451B-A2B2-7BD22E246F6D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="15"/>
@@ -5542,6 +5979,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001F-0AF8-451B-A2B2-7BD22E246F6D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="16"/>
@@ -5573,6 +6015,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000021-0AF8-451B-A2B2-7BD22E246F6D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="17"/>
@@ -5604,6 +6051,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000023-0AF8-451B-A2B2-7BD22E246F6D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="18"/>
@@ -5633,6 +6085,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000025-0AF8-451B-A2B2-7BD22E246F6D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="19"/>
@@ -5662,6 +6119,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000027-0AF8-451B-A2B2-7BD22E246F6D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="20"/>
@@ -5691,6 +6153,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000029-0AF8-451B-A2B2-7BD22E246F6D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="21"/>
@@ -5720,6 +6187,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000002B-0AF8-451B-A2B2-7BD22E246F6D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="22"/>
@@ -5749,6 +6221,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000002D-0AF8-451B-A2B2-7BD22E246F6D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="23"/>
@@ -5778,6 +6255,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000002F-0AF8-451B-A2B2-7BD22E246F6D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="24"/>
@@ -5809,6 +6291,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000031-0AF8-451B-A2B2-7BD22E246F6D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="25"/>
@@ -5840,6 +6327,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000033-0AF8-451B-A2B2-7BD22E246F6D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="26"/>
@@ -5871,6 +6363,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000035-0AF8-451B-A2B2-7BD22E246F6D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="27"/>
@@ -5902,6 +6399,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000037-0AF8-451B-A2B2-7BD22E246F6D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="28"/>
@@ -5933,6 +6435,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000039-0AF8-451B-A2B2-7BD22E246F6D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="29"/>
@@ -5964,6 +6471,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000003B-0AF8-451B-A2B2-7BD22E246F6D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>
@@ -6253,6 +6765,216 @@
       <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IN"/>
+              <a:t>Histogram</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Frequency</c:v>
+          </c:tx>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>[2]Sheet1!$A$2:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>More</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>[2]Sheet1!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3682-497B-841F-8CE1FF5DF4D1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="1876093536"/>
+        <c:axId val="1876097856"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1876093536"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-IN"/>
+                  <a:t>Bin</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1876097856"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1876097856"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-IN"/>
+                  <a:t>Frequency</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1876093536"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
@@ -9964,15 +10686,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>33</xdr:col>
-      <xdr:colOff>504825</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>185737</xdr:rowOff>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>23812</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>41</xdr:col>
-      <xdr:colOff>200025</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>71437</xdr:rowOff>
+      <xdr:rowOff>100012</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -9997,7 +10719,345 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Chart 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F6D293E4-32F1-4C0B-ADFF-7B17BE04C6B5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="A2">
+            <v>18.95</v>
+          </cell>
+          <cell r="B2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3">
+            <v>19.8</v>
+          </cell>
+          <cell r="B3">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4">
+            <v>20.149999999999999</v>
+          </cell>
+          <cell r="B4">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5">
+            <v>20.65</v>
+          </cell>
+          <cell r="B5">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6">
+            <v>29.75</v>
+          </cell>
+          <cell r="B6">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7">
+            <v>30.2</v>
+          </cell>
+          <cell r="B7">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8">
+            <v>39.65</v>
+          </cell>
+          <cell r="B8">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9">
+            <v>42.3</v>
+          </cell>
+          <cell r="B9">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10">
+            <v>49.95</v>
+          </cell>
+          <cell r="B10">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11">
+            <v>53.85</v>
+          </cell>
+          <cell r="B11">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12">
+            <v>55.2</v>
+          </cell>
+          <cell r="B12">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13">
+            <v>55.3</v>
+          </cell>
+          <cell r="B13">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14">
+            <v>56.15</v>
+          </cell>
+          <cell r="B14">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15">
+            <v>59.6</v>
+          </cell>
+          <cell r="B15">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16">
+            <v>59.9</v>
+          </cell>
+          <cell r="B16">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17">
+            <v>70.7</v>
+          </cell>
+          <cell r="B17">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18">
+            <v>89.1</v>
+          </cell>
+          <cell r="B18">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="A19">
+            <v>90.05</v>
+          </cell>
+          <cell r="B19">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="A20">
+            <v>90.25</v>
+          </cell>
+          <cell r="B20">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="A21">
+            <v>99.35</v>
+          </cell>
+          <cell r="B21">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="A22">
+            <v>99.65</v>
+          </cell>
+          <cell r="B22">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="A23">
+            <v>100.35</v>
+          </cell>
+          <cell r="B23">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="A24">
+            <v>103.7</v>
+          </cell>
+          <cell r="B24">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="A25">
+            <v>104.8</v>
+          </cell>
+          <cell r="B25">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="A26">
+            <v>105.5</v>
+          </cell>
+          <cell r="B26">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="A27">
+            <v>106.7</v>
+          </cell>
+          <cell r="B27">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="A28">
+            <v>113.25</v>
+          </cell>
+          <cell r="B28">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="A29" t="str">
+            <v>More</v>
+          </cell>
+          <cell r="B29">
+            <v>23</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="A2">
+            <v>2000</v>
+          </cell>
+          <cell r="B2">
+            <v>18</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3">
+            <v>2000</v>
+          </cell>
+          <cell r="B3">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4">
+            <v>5000</v>
+          </cell>
+          <cell r="B4">
+            <v>6</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5">
+            <v>6000</v>
+          </cell>
+          <cell r="B5">
+            <v>2</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6">
+            <v>8000</v>
+          </cell>
+          <cell r="B6">
+            <v>3</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7" t="str">
+            <v>More</v>
+          </cell>
+          <cell r="B7">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10296,8 +11356,818 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD945AEC-670A-4099-8920-DF5FCF77E608}">
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="D4" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="E4" s="28" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="26">
+        <v>29</v>
+      </c>
+      <c r="C5" s="26">
+        <v>1871.6000000000004</v>
+      </c>
+      <c r="D5" s="26">
+        <v>64.537931034482767</v>
+      </c>
+      <c r="E5" s="26">
+        <v>1000.701724137929</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" s="27">
+        <v>29</v>
+      </c>
+      <c r="C6" s="27">
+        <v>66051.850000000006</v>
+      </c>
+      <c r="D6" s="27">
+        <v>2277.65</v>
+      </c>
+      <c r="E6" s="27">
+        <v>5575432.8303571409</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="B10" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="D10" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="E10" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="F10" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="G10" s="28" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="B11" s="26">
+        <v>71019042.932112128</v>
+      </c>
+      <c r="C11" s="26">
+        <v>1</v>
+      </c>
+      <c r="D11" s="26">
+        <v>71019042.932112128</v>
+      </c>
+      <c r="E11" s="26">
+        <v>25.471134022682723</v>
+      </c>
+      <c r="F11" s="26">
+        <v>5.0625423648206887E-6</v>
+      </c>
+      <c r="G11" s="26">
+        <v>4.0129733776501437</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="B12" s="26">
+        <v>156140138.89827582</v>
+      </c>
+      <c r="C12" s="26">
+        <v>56</v>
+      </c>
+      <c r="D12" s="26">
+        <v>2788216.7660406395</v>
+      </c>
+      <c r="E12" s="26"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="26"/>
+      <c r="B13" s="26"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="26"/>
+    </row>
+    <row r="14" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="B14" s="27">
+        <v>227159181.83038795</v>
+      </c>
+      <c r="C14" s="27">
+        <v>57</v>
+      </c>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="27"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B8A345B-5118-4F68-A8E0-6F8AB96563A7}">
+  <dimension ref="A1:I53"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="31" t="s">
+        <v>99</v>
+      </c>
+      <c r="B3" s="31"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="B4" s="26">
+        <v>0.74392650602795662</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="B5" s="26">
+        <v>0.55342664637096339</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="B6" s="26">
+        <v>0.53688689253285093</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" s="26">
+        <v>21.527612155398263</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="B8" s="27">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="28"/>
+      <c r="B11" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="D11" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="E11" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="F11" s="28" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="B12" s="26">
+        <v>1</v>
+      </c>
+      <c r="C12" s="26">
+        <v>15506.819977804294</v>
+      </c>
+      <c r="D12" s="26">
+        <v>15506.819977804294</v>
+      </c>
+      <c r="E12" s="26">
+        <v>33.460391961560234</v>
+      </c>
+      <c r="F12" s="26">
+        <v>3.7400064804862511E-6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="B13" s="26">
+        <v>27</v>
+      </c>
+      <c r="C13" s="26">
+        <v>12512.828298057779</v>
+      </c>
+      <c r="D13" s="26">
+        <v>463.43808511325108</v>
+      </c>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+    </row>
+    <row r="14" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="B14" s="27">
+        <v>28</v>
+      </c>
+      <c r="C14" s="27">
+        <v>28019.648275862073</v>
+      </c>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
+    </row>
+    <row r="15" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="28"/>
+      <c r="B16" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="C16" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="E16" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="F16" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="G16" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="H16" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="I16" s="28" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="B17" s="26">
+        <v>41.837711832724665</v>
+      </c>
+      <c r="C17" s="26">
+        <v>5.6018675424379181</v>
+      </c>
+      <c r="D17" s="26">
+        <v>7.4685292923789843</v>
+      </c>
+      <c r="E17" s="26">
+        <v>4.9257000454046131E-8</v>
+      </c>
+      <c r="F17" s="26">
+        <v>30.343629059870121</v>
+      </c>
+      <c r="G17" s="26">
+        <v>53.331794605579205</v>
+      </c>
+      <c r="H17" s="26">
+        <v>30.343629059870121</v>
+      </c>
+      <c r="I17" s="26">
+        <v>53.331794605579205</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="B18" s="27">
+        <v>9.9665089903005731E-3</v>
+      </c>
+      <c r="C18" s="27">
+        <v>1.7229693459923743E-3</v>
+      </c>
+      <c r="D18" s="27">
+        <v>5.7844958260474382</v>
+      </c>
+      <c r="E18" s="27">
+        <v>3.7400064804862511E-6</v>
+      </c>
+      <c r="F18" s="27">
+        <v>6.4312679072333397E-3</v>
+      </c>
+      <c r="G18" s="27">
+        <v>1.3501750073367806E-2</v>
+      </c>
+      <c r="H18" s="27">
+        <v>6.4312679072333397E-3</v>
+      </c>
+      <c r="I18" s="27">
+        <v>1.3501750073367806E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="B24" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="C24" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="D24" s="28" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="26">
+        <v>1</v>
+      </c>
+      <c r="B25" s="26">
+        <v>42.135212126085136</v>
+      </c>
+      <c r="C25" s="26">
+        <v>-12.285212126085135</v>
+      </c>
+      <c r="D25" s="26">
+        <v>-0.58114423353376099</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="26">
+        <v>2</v>
+      </c>
+      <c r="B26" s="26">
+        <v>60.6694305698976</v>
+      </c>
+      <c r="C26" s="26">
+        <v>-3.7194305698975967</v>
+      </c>
+      <c r="D26" s="26">
+        <v>-0.1759453239831017</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="26">
+        <v>3</v>
+      </c>
+      <c r="B27" s="26">
+        <v>42.91558978002567</v>
+      </c>
+      <c r="C27" s="26">
+        <v>10.934410219974332</v>
+      </c>
+      <c r="D27" s="26">
+        <v>0.51724539887579879</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="26">
+        <v>4</v>
+      </c>
+      <c r="B28" s="26">
+        <v>60.183563256620445</v>
+      </c>
+      <c r="C28" s="26">
+        <v>-17.883563256620448</v>
+      </c>
+      <c r="D28" s="26">
+        <v>-0.84597071299680371</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="26">
+        <v>5</v>
+      </c>
+      <c r="B29" s="26">
+        <v>43.349132921103745</v>
+      </c>
+      <c r="C29" s="26">
+        <v>27.350867078896258</v>
+      </c>
+      <c r="D29" s="26">
+        <v>1.2938155663832283</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="26">
+        <v>6</v>
+      </c>
+      <c r="B30" s="26">
+        <v>50.015232459266286</v>
+      </c>
+      <c r="C30" s="26">
+        <v>49.634767540733719</v>
+      </c>
+      <c r="D30" s="26">
+        <v>2.3479414635291258</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="26">
+        <v>7</v>
+      </c>
+      <c r="B31" s="26">
+        <v>61.266424458416601</v>
+      </c>
+      <c r="C31" s="26">
+        <v>27.833575541583393</v>
+      </c>
+      <c r="D31" s="26">
+        <v>1.3166497866384033</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="26">
+        <v>8</v>
+      </c>
+      <c r="B32" s="26">
+        <v>44.846600896896405</v>
+      </c>
+      <c r="C32" s="26">
+        <v>-15.096600896896405</v>
+      </c>
+      <c r="D32" s="26">
+        <v>-0.71413521127271673</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="26">
+        <v>9</v>
+      </c>
+      <c r="B33" s="26">
+        <v>72.196196542629735</v>
+      </c>
+      <c r="C33" s="26">
+        <v>32.603803457370262</v>
+      </c>
+      <c r="D33" s="26">
+        <v>1.5423024182291212</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="26">
+        <v>10</v>
+      </c>
+      <c r="B34" s="26">
+        <v>76.600396865443543</v>
+      </c>
+      <c r="C34" s="26">
+        <v>-20.450396865443544</v>
+      </c>
+      <c r="D34" s="26">
+        <v>-0.96739316259707353</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="26">
+        <v>11</v>
+      </c>
+      <c r="B35" s="26">
+        <v>47.692537539076739</v>
+      </c>
+      <c r="C35" s="26">
+        <v>2.2574624609232643</v>
+      </c>
+      <c r="D35" s="26">
+        <v>0.10678784201038849</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="26">
+        <v>12</v>
+      </c>
+      <c r="B36" s="26">
+        <v>45.09476697075489</v>
+      </c>
+      <c r="C36" s="26">
+        <v>-26.14476697075489</v>
+      </c>
+      <c r="D36" s="26">
+        <v>-1.2367617592761824</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="26">
+        <v>13</v>
+      </c>
+      <c r="B37" s="26">
+        <v>98.458446057521257</v>
+      </c>
+      <c r="C37" s="26">
+        <v>1.8915539424787369</v>
+      </c>
+      <c r="D37" s="26">
+        <v>8.9478769662878155E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="26">
+        <v>14</v>
+      </c>
+      <c r="B38" s="26">
+        <v>92.032041060575438</v>
+      </c>
+      <c r="C38" s="26">
+        <v>11.667958939424565</v>
+      </c>
+      <c r="D38" s="26">
+        <v>0.55194545972533204</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="26">
+        <v>15</v>
+      </c>
+      <c r="B39" s="26">
+        <v>68.608253306121526</v>
+      </c>
+      <c r="C39" s="26">
+        <v>36.891746693878474</v>
+      </c>
+      <c r="D39" s="26">
+        <v>1.7451408763722875</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="26">
+        <v>16</v>
+      </c>
+      <c r="B40" s="26">
+        <v>120.52479528749623</v>
+      </c>
+      <c r="C40" s="26">
+        <v>-7.2747952874962323</v>
+      </c>
+      <c r="D40" s="26">
+        <v>-0.34412961600315772</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="26">
+        <v>17</v>
+      </c>
+      <c r="B41" s="26">
+        <v>52.03295220435264</v>
+      </c>
+      <c r="C41" s="26">
+        <v>-31.382952204352641</v>
+      </c>
+      <c r="D41" s="26">
+        <v>-1.4845508174906041</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="26">
+        <v>18</v>
+      </c>
+      <c r="B42" s="26">
+        <v>115.41297282637107</v>
+      </c>
+      <c r="C42" s="26">
+        <v>-8.7129728263710717</v>
+      </c>
+      <c r="D42" s="26">
+        <v>-0.41216170001905056</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="26">
+        <v>19</v>
+      </c>
+      <c r="B43" s="26">
+        <v>47.103516857749973</v>
+      </c>
+      <c r="C43" s="26">
+        <v>8.0964831422500296</v>
+      </c>
+      <c r="D43" s="26">
+        <v>0.38299904321809214</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="26">
+        <v>20</v>
+      </c>
+      <c r="B44" s="26">
+        <v>60.404321430755601</v>
+      </c>
+      <c r="C44" s="26">
+        <v>29.645678569244396</v>
+      </c>
+      <c r="D44" s="26">
+        <v>1.4023701807419966</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="26">
+        <v>21</v>
+      </c>
+      <c r="B45" s="26">
+        <v>42.232883914190083</v>
+      </c>
+      <c r="C45" s="26">
+        <v>-2.5828839141900843</v>
+      </c>
+      <c r="D45" s="26">
+        <v>-0.12218169920172163</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="26">
+        <v>22</v>
+      </c>
+      <c r="B46" s="26">
+        <v>43.853438276012959</v>
+      </c>
+      <c r="C46" s="26">
+        <v>-24.053438276012958</v>
+      </c>
+      <c r="D46" s="26">
+        <v>-1.1378327705945475</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="26">
+        <v>23</v>
+      </c>
+      <c r="B47" s="26">
+        <v>42.038536988879223</v>
+      </c>
+      <c r="C47" s="26">
+        <v>-21.888536988879224</v>
+      </c>
+      <c r="D47" s="26">
+        <v>-1.0354234766991472</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="26">
+        <v>24</v>
+      </c>
+      <c r="B48" s="26">
+        <v>76.771322494627199</v>
+      </c>
+      <c r="C48" s="26">
+        <v>-16.871322494627201</v>
+      </c>
+      <c r="D48" s="26">
+        <v>-0.79808730034240194</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="26">
+        <v>25</v>
+      </c>
+      <c r="B49" s="26">
+        <v>71.441233486614465</v>
+      </c>
+      <c r="C49" s="26">
+        <v>-11.841233486614463</v>
+      </c>
+      <c r="D49" s="26">
+        <v>-0.56014210320890467</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="26">
+        <v>26</v>
+      </c>
+      <c r="B50" s="26">
+        <v>57.092450493278719</v>
+      </c>
+      <c r="C50" s="26">
+        <v>-1.7924504932787215</v>
+      </c>
+      <c r="D50" s="26">
+        <v>-8.4790743323991655E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="26">
+        <v>27</v>
+      </c>
+      <c r="B51" s="26">
+        <v>89.170158004010631</v>
+      </c>
+      <c r="C51" s="26">
+        <v>10.179841995989364</v>
+      </c>
+      <c r="D51" s="26">
+        <v>0.48155102358328084</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="26">
+        <v>28</v>
+      </c>
+      <c r="B52" s="26">
+        <v>42.138700404231741</v>
+      </c>
+      <c r="C52" s="26">
+        <v>-11.938700404231742</v>
+      </c>
+      <c r="D52" s="26">
+        <v>-0.56475271445047392</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="27">
+        <v>29</v>
+      </c>
+      <c r="B53" s="27">
+        <v>105.31889252099465</v>
+      </c>
+      <c r="C53" s="27">
+        <v>-15.068892520994652</v>
+      </c>
+      <c r="D53" s="27">
+        <v>-0.71282448397630327</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{845BF07B-C546-4D3C-A0E6-EF89EFB33582}">
-  <dimension ref="A1:T53"/>
+  <dimension ref="A1:BA64"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
@@ -10316,9 +12186,18 @@
     <col min="14" max="14" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="8.28515625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="13.140625" customWidth="1"/>
+    <col min="43" max="43" width="18" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="12" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="12" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="12" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:53" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -10367,12 +12246,14 @@
       <c r="P1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="Q1" s="15"/>
+      <c r="Q1" s="15" t="s">
+        <v>97</v>
+      </c>
       <c r="R1" s="15"/>
       <c r="S1" s="15"/>
       <c r="T1" s="15"/>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -10420,14 +12301,19 @@
       </c>
       <c r="P2">
         <f ca="1">RANDBETWEEN(500000,599999)</f>
-        <v>510959</v>
-      </c>
-      <c r="Q2" s="16"/>
+        <v>568889</v>
+      </c>
+      <c r="Q2" s="16">
+        <v>5000</v>
+      </c>
       <c r="R2" s="18"/>
       <c r="S2" s="17"/>
       <c r="T2" s="19"/>
+      <c r="BA2">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -10475,14 +12361,16 @@
       </c>
       <c r="P3">
         <f t="shared" ref="P3:P30" ca="1" si="0">RANDBETWEEN(500000,599999)</f>
-        <v>538145</v>
-      </c>
-      <c r="Q3" s="16"/>
+        <v>528570</v>
+      </c>
+      <c r="Q3" s="16">
+        <v>2000</v>
+      </c>
       <c r="R3" s="18"/>
       <c r="S3" s="17"/>
       <c r="T3" s="19"/>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -10530,14 +12418,16 @@
       </c>
       <c r="P4">
         <f t="shared" ca="1" si="0"/>
-        <v>568241</v>
-      </c>
-      <c r="Q4" s="16"/>
+        <v>542485</v>
+      </c>
+      <c r="Q4" s="16">
+        <v>3000</v>
+      </c>
       <c r="R4" s="18"/>
       <c r="S4" s="17"/>
       <c r="T4" s="19"/>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>26</v>
       </c>
@@ -10585,14 +12475,19 @@
       </c>
       <c r="P5">
         <f t="shared" ca="1" si="0"/>
-        <v>571948</v>
-      </c>
-      <c r="Q5" s="16"/>
+        <v>587693</v>
+      </c>
+      <c r="Q5" s="16">
+        <v>6000</v>
+      </c>
       <c r="R5" s="18"/>
       <c r="S5" s="17"/>
       <c r="T5" s="19"/>
+      <c r="AQ5" t="s">
+        <v>98</v>
+      </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:53" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>28</v>
       </c>
@@ -10640,14 +12535,16 @@
       </c>
       <c r="P6">
         <f t="shared" ca="1" si="0"/>
-        <v>564565</v>
-      </c>
-      <c r="Q6" s="16"/>
+        <v>534143</v>
+      </c>
+      <c r="Q6" s="16">
+        <v>8000</v>
+      </c>
       <c r="R6" s="18"/>
       <c r="S6" s="17"/>
       <c r="T6" s="19"/>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -10695,14 +12592,18 @@
       </c>
       <c r="P7">
         <f t="shared" ca="1" si="0"/>
-        <v>580122</v>
+        <v>575339</v>
       </c>
       <c r="Q7" s="16"/>
       <c r="R7" s="18"/>
       <c r="S7" s="17"/>
       <c r="T7" s="19"/>
+      <c r="AQ7" s="31" t="s">
+        <v>99</v>
+      </c>
+      <c r="AR7" s="31"/>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>31</v>
       </c>
@@ -10750,14 +12651,20 @@
       </c>
       <c r="P8">
         <f t="shared" ca="1" si="0"/>
-        <v>516124</v>
+        <v>525835</v>
       </c>
       <c r="Q8" s="16"/>
       <c r="R8" s="18"/>
       <c r="S8" s="17"/>
       <c r="T8" s="19"/>
+      <c r="AQ8" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="AR8" s="26">
+        <v>0.74392650602795662</v>
+      </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>33</v>
       </c>
@@ -10805,14 +12712,20 @@
       </c>
       <c r="P9">
         <f t="shared" ca="1" si="0"/>
-        <v>511225</v>
+        <v>539920</v>
       </c>
       <c r="Q9" s="16"/>
       <c r="R9" s="18"/>
       <c r="S9" s="17"/>
       <c r="T9" s="19"/>
+      <c r="AQ9" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="AR9" s="26">
+        <v>0.55342664637096339</v>
+      </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>34</v>
       </c>
@@ -10860,14 +12773,20 @@
       </c>
       <c r="P10">
         <f t="shared" ca="1" si="0"/>
-        <v>569774</v>
+        <v>516361</v>
       </c>
       <c r="Q10" s="16"/>
       <c r="R10" s="18"/>
       <c r="S10" s="17"/>
       <c r="T10" s="19"/>
+      <c r="AQ10" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="AR10" s="26">
+        <v>0.53688689253285093</v>
+      </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>35</v>
       </c>
@@ -10915,14 +12834,20 @@
       </c>
       <c r="P11">
         <f t="shared" ca="1" si="0"/>
-        <v>556456</v>
+        <v>598341</v>
       </c>
       <c r="Q11" s="16"/>
       <c r="R11" s="18"/>
       <c r="S11" s="17"/>
       <c r="T11" s="19"/>
+      <c r="AQ11" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="AR11" s="26">
+        <v>21.527612155398263</v>
+      </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:53" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>36</v>
       </c>
@@ -10970,14 +12895,20 @@
       </c>
       <c r="P12">
         <f t="shared" ca="1" si="0"/>
-        <v>581168</v>
+        <v>524749</v>
       </c>
       <c r="Q12" s="16"/>
       <c r="R12" s="18"/>
       <c r="S12" s="17"/>
       <c r="T12" s="19"/>
+      <c r="AQ12" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="AR12" s="27">
+        <v>29</v>
+      </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -11025,14 +12956,14 @@
       </c>
       <c r="P13">
         <f t="shared" ca="1" si="0"/>
-        <v>528846</v>
+        <v>530291</v>
       </c>
       <c r="Q13" s="16"/>
       <c r="R13" s="18"/>
       <c r="S13" s="17"/>
       <c r="T13" s="19"/>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:53" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -11080,14 +13011,17 @@
       </c>
       <c r="P14">
         <f t="shared" ca="1" si="0"/>
-        <v>549625</v>
+        <v>515539</v>
       </c>
       <c r="Q14" s="16"/>
       <c r="R14" s="18"/>
       <c r="S14" s="17"/>
       <c r="T14" s="19"/>
+      <c r="AQ14" t="s">
+        <v>86</v>
+      </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -11135,14 +13069,30 @@
       </c>
       <c r="P15">
         <f t="shared" ca="1" si="0"/>
-        <v>517350</v>
+        <v>506837</v>
       </c>
       <c r="Q15" s="16"/>
       <c r="R15" s="18"/>
       <c r="S15" s="17"/>
       <c r="T15" s="19"/>
+      <c r="AQ15" s="28"/>
+      <c r="AR15" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="AS15" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="AT15" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="AU15" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="AV15" s="28" t="s">
+        <v>107</v>
+      </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>41</v>
       </c>
@@ -11190,14 +13140,32 @@
       </c>
       <c r="P16">
         <f t="shared" ca="1" si="0"/>
-        <v>574068</v>
+        <v>568312</v>
       </c>
       <c r="Q16" s="16"/>
       <c r="R16" s="18"/>
       <c r="S16" s="17"/>
       <c r="T16" s="19"/>
+      <c r="AQ16" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="AR16" s="26">
+        <v>1</v>
+      </c>
+      <c r="AS16" s="26">
+        <v>15506.819977804294</v>
+      </c>
+      <c r="AT16" s="26">
+        <v>15506.819977804294</v>
+      </c>
+      <c r="AU16" s="26">
+        <v>33.460391961560234</v>
+      </c>
+      <c r="AV16" s="26">
+        <v>3.7400064804862511E-6</v>
+      </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>42</v>
       </c>
@@ -11245,14 +13213,28 @@
       </c>
       <c r="P17">
         <f t="shared" ca="1" si="0"/>
-        <v>559107</v>
+        <v>529702</v>
       </c>
       <c r="Q17" s="16"/>
       <c r="R17" s="18"/>
       <c r="S17" s="17"/>
       <c r="T17" s="19"/>
+      <c r="AQ17" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="AR17" s="26">
+        <v>27</v>
+      </c>
+      <c r="AS17" s="26">
+        <v>12512.828298057779</v>
+      </c>
+      <c r="AT17" s="26">
+        <v>463.43808511325108</v>
+      </c>
+      <c r="AU17" s="26"/>
+      <c r="AV17" s="26"/>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:51" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>43</v>
       </c>
@@ -11300,14 +13282,26 @@
       </c>
       <c r="P18">
         <f t="shared" ca="1" si="0"/>
-        <v>573138</v>
+        <v>500720</v>
       </c>
       <c r="Q18" s="16"/>
       <c r="R18" s="18"/>
       <c r="S18" s="17"/>
       <c r="T18" s="19"/>
+      <c r="AQ18" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="AR18" s="27">
+        <v>28</v>
+      </c>
+      <c r="AS18" s="27">
+        <v>28019.648275862073</v>
+      </c>
+      <c r="AT18" s="27"/>
+      <c r="AU18" s="27"/>
+      <c r="AV18" s="27"/>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:51" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -11355,14 +13349,14 @@
       </c>
       <c r="P19">
         <f t="shared" ca="1" si="0"/>
-        <v>595209</v>
+        <v>554194</v>
       </c>
       <c r="Q19" s="16"/>
       <c r="R19" s="18"/>
       <c r="S19" s="17"/>
       <c r="T19" s="19"/>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>45</v>
       </c>
@@ -11410,14 +13404,39 @@
       </c>
       <c r="P20">
         <f t="shared" ca="1" si="0"/>
-        <v>580002</v>
+        <v>509430</v>
       </c>
       <c r="Q20" s="16"/>
       <c r="R20" s="18"/>
       <c r="S20" s="17"/>
       <c r="T20" s="19"/>
+      <c r="AQ20" s="28"/>
+      <c r="AR20" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="AS20" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="AT20" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="AU20" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="AV20" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="AW20" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="AX20" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="AY20" s="28" t="s">
+        <v>113</v>
+      </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>46</v>
       </c>
@@ -11465,14 +13484,41 @@
       </c>
       <c r="P21">
         <f t="shared" ca="1" si="0"/>
-        <v>563644</v>
+        <v>543981</v>
       </c>
       <c r="Q21" s="16"/>
       <c r="R21" s="18"/>
       <c r="S21" s="17"/>
       <c r="T21" s="19"/>
+      <c r="AQ21" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="AR21" s="26">
+        <v>41.837711832724665</v>
+      </c>
+      <c r="AS21" s="26">
+        <v>5.6018675424379181</v>
+      </c>
+      <c r="AT21" s="26">
+        <v>7.4685292923789843</v>
+      </c>
+      <c r="AU21" s="26">
+        <v>4.9257000454046131E-8</v>
+      </c>
+      <c r="AV21" s="26">
+        <v>30.343629059870121</v>
+      </c>
+      <c r="AW21" s="26">
+        <v>53.331794605579205</v>
+      </c>
+      <c r="AX21" s="26">
+        <v>30.343629059870121</v>
+      </c>
+      <c r="AY21" s="26">
+        <v>53.331794605579205</v>
+      </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:51" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>47</v>
       </c>
@@ -11520,14 +13566,41 @@
       </c>
       <c r="P22">
         <f t="shared" ca="1" si="0"/>
-        <v>511466</v>
+        <v>545125</v>
       </c>
       <c r="Q22" s="16"/>
       <c r="R22" s="18"/>
       <c r="S22" s="17"/>
       <c r="T22" s="19"/>
+      <c r="AQ22" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="AR22" s="27">
+        <v>9.9665089903005731E-3</v>
+      </c>
+      <c r="AS22" s="27">
+        <v>1.7229693459923743E-3</v>
+      </c>
+      <c r="AT22" s="27">
+        <v>5.7844958260474382</v>
+      </c>
+      <c r="AU22" s="27">
+        <v>3.7400064804862511E-6</v>
+      </c>
+      <c r="AV22" s="27">
+        <v>6.4312679072333397E-3</v>
+      </c>
+      <c r="AW22" s="27">
+        <v>1.3501750073367806E-2</v>
+      </c>
+      <c r="AX22" s="27">
+        <v>6.4312679072333397E-3</v>
+      </c>
+      <c r="AY22" s="27">
+        <v>1.3501750073367806E-2</v>
+      </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>48</v>
       </c>
@@ -11575,14 +13648,14 @@
       </c>
       <c r="P23">
         <f t="shared" ca="1" si="0"/>
-        <v>514463</v>
+        <v>538621</v>
       </c>
       <c r="Q23" s="16"/>
       <c r="R23" s="18"/>
       <c r="S23" s="17"/>
       <c r="T23" s="19"/>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>49</v>
       </c>
@@ -11630,14 +13703,14 @@
       </c>
       <c r="P24">
         <f t="shared" ca="1" si="0"/>
-        <v>527021</v>
+        <v>515503</v>
       </c>
       <c r="Q24" s="16"/>
       <c r="R24" s="18"/>
       <c r="S24" s="17"/>
       <c r="T24" s="19"/>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>50</v>
       </c>
@@ -11685,14 +13758,14 @@
       </c>
       <c r="P25">
         <f t="shared" ca="1" si="0"/>
-        <v>589750</v>
+        <v>525936</v>
       </c>
       <c r="Q25" s="16"/>
       <c r="R25" s="18"/>
       <c r="S25" s="17"/>
       <c r="T25" s="19"/>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>51</v>
       </c>
@@ -11740,14 +13813,17 @@
       </c>
       <c r="P26">
         <f t="shared" ca="1" si="0"/>
-        <v>584995</v>
+        <v>553223</v>
       </c>
       <c r="Q26" s="16"/>
       <c r="R26" s="18"/>
       <c r="S26" s="17"/>
       <c r="T26" s="19"/>
+      <c r="AQ26" t="s">
+        <v>115</v>
+      </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:51" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>52</v>
       </c>
@@ -11795,14 +13871,14 @@
       </c>
       <c r="P27">
         <f t="shared" ca="1" si="0"/>
-        <v>545258</v>
+        <v>552509</v>
       </c>
       <c r="Q27" s="16"/>
       <c r="R27" s="18"/>
       <c r="S27" s="17"/>
       <c r="T27" s="19"/>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>53</v>
       </c>
@@ -11850,14 +13926,26 @@
       </c>
       <c r="P28">
         <f t="shared" ca="1" si="0"/>
-        <v>503674</v>
+        <v>522056</v>
       </c>
       <c r="Q28" s="16"/>
       <c r="R28" s="18"/>
       <c r="S28" s="17"/>
       <c r="T28" s="19"/>
+      <c r="AQ28" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="AR28" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="AS28" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="AT28" s="28" t="s">
+        <v>119</v>
+      </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>54</v>
       </c>
@@ -11905,14 +13993,26 @@
       </c>
       <c r="P29">
         <f t="shared" ca="1" si="0"/>
-        <v>523767</v>
+        <v>539927</v>
       </c>
       <c r="Q29" s="16"/>
       <c r="R29" s="18"/>
       <c r="S29" s="17"/>
       <c r="T29" s="19"/>
+      <c r="AQ29" s="26">
+        <v>1</v>
+      </c>
+      <c r="AR29" s="26">
+        <v>42.135212126085136</v>
+      </c>
+      <c r="AS29" s="26">
+        <v>-12.285212126085135</v>
+      </c>
+      <c r="AT29" s="26">
+        <v>-0.58114423353376099</v>
+      </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>55</v>
       </c>
@@ -11960,20 +14060,72 @@
       </c>
       <c r="P30">
         <f t="shared" ca="1" si="0"/>
-        <v>521931</v>
+        <v>570005</v>
       </c>
       <c r="Q30" s="16"/>
       <c r="R30" s="18"/>
       <c r="S30" s="17"/>
       <c r="T30" s="19"/>
+      <c r="AQ30" s="26">
+        <v>2</v>
+      </c>
+      <c r="AR30" s="26">
+        <v>60.6694305698976</v>
+      </c>
+      <c r="AS30" s="26">
+        <v>-3.7194305698975967</v>
+      </c>
+      <c r="AT30" s="26">
+        <v>-0.1759453239831017</v>
+      </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:51" x14ac:dyDescent="0.25">
       <c r="I31" s="11"/>
       <c r="N31" s="7"/>
       <c r="Q31" s="13"/>
       <c r="T31" s="19"/>
+      <c r="AQ31" s="26">
+        <v>3</v>
+      </c>
+      <c r="AR31" s="26">
+        <v>42.91558978002567</v>
+      </c>
+      <c r="AS31" s="26">
+        <v>10.934410219974332</v>
+      </c>
+      <c r="AT31" s="26">
+        <v>0.51724539887579879</v>
+      </c>
     </row>
-    <row r="34" spans="7:10" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AQ32" s="26">
+        <v>4</v>
+      </c>
+      <c r="AR32" s="26">
+        <v>60.183563256620445</v>
+      </c>
+      <c r="AS32" s="26">
+        <v>-17.883563256620448</v>
+      </c>
+      <c r="AT32" s="26">
+        <v>-0.84597071299680371</v>
+      </c>
+    </row>
+    <row r="33" spans="7:46" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="AQ33" s="26">
+        <v>5</v>
+      </c>
+      <c r="AR33" s="26">
+        <v>43.349132921103745</v>
+      </c>
+      <c r="AS33" s="26">
+        <v>27.350867078896258</v>
+      </c>
+      <c r="AT33" s="26">
+        <v>1.2938155663832283</v>
+      </c>
+    </row>
+    <row r="34" spans="7:46" ht="18.75" x14ac:dyDescent="0.4">
       <c r="G34" s="20" t="s">
         <v>57</v>
       </c>
@@ -11986,8 +14138,27 @@
       <c r="J34" s="21" t="s">
         <v>60</v>
       </c>
+      <c r="L34" s="28"/>
+      <c r="M34" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="N34" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="AQ34" s="26">
+        <v>6</v>
+      </c>
+      <c r="AR34" s="26">
+        <v>50.015232459266286</v>
+      </c>
+      <c r="AS34" s="26">
+        <v>49.634767540733719</v>
+      </c>
+      <c r="AT34" s="26">
+        <v>2.3479414635291258</v>
+      </c>
     </row>
-    <row r="35" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="7:46" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G35" s="22">
         <v>-65</v>
       </c>
@@ -12000,8 +14171,27 @@
       <c r="J35" s="25">
         <v>-65</v>
       </c>
+      <c r="L35" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="M35" s="26">
+        <v>1</v>
+      </c>
+      <c r="N35" s="26"/>
+      <c r="AQ35" s="26">
+        <v>7</v>
+      </c>
+      <c r="AR35" s="26">
+        <v>61.266424458416601</v>
+      </c>
+      <c r="AS35" s="26">
+        <v>27.833575541583393</v>
+      </c>
+      <c r="AT35" s="26">
+        <v>1.3166497866384033</v>
+      </c>
     </row>
-    <row r="36" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="7:46" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G36" s="22">
         <v>-45</v>
       </c>
@@ -12014,8 +14204,35 @@
       <c r="J36" s="25">
         <v>-45</v>
       </c>
+      <c r="L36" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="M36" s="27">
+        <v>0.74392650602795651</v>
+      </c>
+      <c r="N36" s="27">
+        <v>1</v>
+      </c>
+      <c r="R36" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="S36" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="AQ36" s="26">
+        <v>8</v>
+      </c>
+      <c r="AR36" s="26">
+        <v>44.846600896896405</v>
+      </c>
+      <c r="AS36" s="26">
+        <v>-15.096600896896405</v>
+      </c>
+      <c r="AT36" s="26">
+        <v>-0.71413521127271673</v>
+      </c>
     </row>
-    <row r="37" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="7:46" x14ac:dyDescent="0.25">
       <c r="G37" s="22">
         <v>81</v>
       </c>
@@ -12028,8 +14245,29 @@
       <c r="J37" s="25">
         <v>81</v>
       </c>
+      <c r="R37" s="16">
+        <v>2000</v>
+      </c>
+      <c r="S37">
+        <v>18</v>
+      </c>
+      <c r="AD37" t="s">
+        <v>81</v>
+      </c>
+      <c r="AQ37" s="26">
+        <v>9</v>
+      </c>
+      <c r="AR37" s="26">
+        <v>72.196196542629735</v>
+      </c>
+      <c r="AS37" s="26">
+        <v>32.603803457370262</v>
+      </c>
+      <c r="AT37" s="26">
+        <v>1.5423024182291212</v>
+      </c>
     </row>
-    <row r="38" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="7:46" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G38" s="22">
         <v>61</v>
       </c>
@@ -12042,8 +14280,26 @@
       <c r="J38" s="25">
         <v>61</v>
       </c>
+      <c r="R38" s="16">
+        <v>3000</v>
+      </c>
+      <c r="S38">
+        <v>0</v>
+      </c>
+      <c r="AQ38" s="26">
+        <v>10</v>
+      </c>
+      <c r="AR38" s="26">
+        <v>76.600396865443543</v>
+      </c>
+      <c r="AS38" s="26">
+        <v>-20.450396865443544</v>
+      </c>
+      <c r="AT38" s="26">
+        <v>-0.96739316259707353</v>
+      </c>
     </row>
-    <row r="39" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="7:46" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G39" s="22">
         <v>0</v>
       </c>
@@ -12056,8 +14312,37 @@
       <c r="J39" s="25">
         <v>0</v>
       </c>
+      <c r="L39" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="M39" s="28"/>
+      <c r="N39" s="28" t="s">
+        <v>64</v>
+      </c>
+      <c r="O39" s="28"/>
+      <c r="R39" s="16">
+        <v>5000</v>
+      </c>
+      <c r="S39">
+        <v>6</v>
+      </c>
+      <c r="AD39" t="s">
+        <v>82</v>
+      </c>
+      <c r="AQ39" s="26">
+        <v>11</v>
+      </c>
+      <c r="AR39" s="26">
+        <v>47.692537539076739</v>
+      </c>
+      <c r="AS39" s="26">
+        <v>2.2574624609232643</v>
+      </c>
+      <c r="AT39" s="26">
+        <v>0.10678784201038849</v>
+      </c>
     </row>
-    <row r="40" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="7:46" x14ac:dyDescent="0.25">
       <c r="G40" s="22">
         <v>-89</v>
       </c>
@@ -12070,8 +14355,45 @@
       <c r="J40" s="25">
         <v>-89</v>
       </c>
+      <c r="L40" s="26"/>
+      <c r="M40" s="26"/>
+      <c r="N40" s="26"/>
+      <c r="O40" s="26"/>
+      <c r="R40" s="16">
+        <v>6000</v>
+      </c>
+      <c r="S40">
+        <v>2</v>
+      </c>
+      <c r="AD40" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="AE40" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="AF40" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG40" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH40" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="AQ40" s="26">
+        <v>12</v>
+      </c>
+      <c r="AR40" s="26">
+        <v>45.09476697075489</v>
+      </c>
+      <c r="AS40" s="26">
+        <v>-26.14476697075489</v>
+      </c>
+      <c r="AT40" s="26">
+        <v>-1.2367617592761824</v>
+      </c>
     </row>
-    <row r="41" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="7:46" x14ac:dyDescent="0.25">
       <c r="G41" s="22">
         <v>-92</v>
       </c>
@@ -12084,8 +14406,53 @@
       <c r="J41" s="25">
         <v>-92</v>
       </c>
+      <c r="L41" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="M41" s="26">
+        <v>64.537931034482767</v>
+      </c>
+      <c r="N41" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="O41" s="26">
+        <v>2277.65</v>
+      </c>
+      <c r="R41" s="16">
+        <v>8000</v>
+      </c>
+      <c r="S41">
+        <v>3</v>
+      </c>
+      <c r="AD41" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE41" s="26">
+        <v>29</v>
+      </c>
+      <c r="AF41" s="26">
+        <v>1871.6000000000004</v>
+      </c>
+      <c r="AG41" s="26">
+        <v>64.537931034482767</v>
+      </c>
+      <c r="AH41" s="26">
+        <v>1000.701724137929</v>
+      </c>
+      <c r="AQ41" s="26">
+        <v>13</v>
+      </c>
+      <c r="AR41" s="26">
+        <v>98.458446057521257</v>
+      </c>
+      <c r="AS41" s="26">
+        <v>1.8915539424787369</v>
+      </c>
+      <c r="AT41" s="26">
+        <v>8.9478769662878155E-2</v>
+      </c>
     </row>
-    <row r="42" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="7:46" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G42" s="22">
         <v>-96</v>
       </c>
@@ -12098,8 +14465,53 @@
       <c r="J42" s="25">
         <v>-96</v>
       </c>
+      <c r="L42" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="M42" s="26">
+        <v>5.8742621668390127</v>
+      </c>
+      <c r="N42" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="O42" s="26">
+        <v>438.47041461776399</v>
+      </c>
+      <c r="R42" s="30" t="s">
+        <v>80</v>
+      </c>
+      <c r="S42" s="30">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE42" s="27">
+        <v>29</v>
+      </c>
+      <c r="AF42" s="27">
+        <v>66051.850000000006</v>
+      </c>
+      <c r="AG42" s="27">
+        <v>2277.65</v>
+      </c>
+      <c r="AH42" s="27">
+        <v>5575432.8303571409</v>
+      </c>
+      <c r="AQ42" s="26">
+        <v>14</v>
+      </c>
+      <c r="AR42" s="26">
+        <v>92.032041060575438</v>
+      </c>
+      <c r="AS42" s="26">
+        <v>11.667958939424565</v>
+      </c>
+      <c r="AT42" s="26">
+        <v>0.55194545972533204</v>
+      </c>
     </row>
-    <row r="43" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="7:46" x14ac:dyDescent="0.25">
       <c r="G43" s="22">
         <v>-69</v>
       </c>
@@ -12112,8 +14524,32 @@
       <c r="J43" s="25">
         <v>-69</v>
       </c>
+      <c r="L43" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="M43" s="26">
+        <v>56.95</v>
+      </c>
+      <c r="N43" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="O43" s="26">
+        <v>1840.75</v>
+      </c>
+      <c r="AQ43" s="26">
+        <v>15</v>
+      </c>
+      <c r="AR43" s="26">
+        <v>68.608253306121526</v>
+      </c>
+      <c r="AS43" s="26">
+        <v>36.891746693878474</v>
+      </c>
+      <c r="AT43" s="26">
+        <v>1.7451408763722875</v>
+      </c>
     </row>
-    <row r="44" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="7:46" x14ac:dyDescent="0.25">
       <c r="G44" s="22">
         <v>-88</v>
       </c>
@@ -12126,8 +14562,32 @@
       <c r="J44" s="25">
         <v>-88</v>
       </c>
+      <c r="L44" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="M44" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="N44" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="O44" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ44" s="26">
+        <v>16</v>
+      </c>
+      <c r="AR44" s="26">
+        <v>120.52479528749623</v>
+      </c>
+      <c r="AS44" s="26">
+        <v>-7.2747952874962323</v>
+      </c>
+      <c r="AT44" s="26">
+        <v>-0.34412961600315772</v>
+      </c>
     </row>
-    <row r="45" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="7:46" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G45" s="22">
         <v>31</v>
       </c>
@@ -12140,8 +14600,35 @@
       <c r="J45" s="25">
         <v>31</v>
       </c>
+      <c r="L45" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="M45" s="26">
+        <v>31.633869888743124</v>
+      </c>
+      <c r="N45" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="O45" s="26">
+        <v>2361.2354457692568</v>
+      </c>
+      <c r="AD45" t="s">
+        <v>86</v>
+      </c>
+      <c r="AQ45" s="26">
+        <v>17</v>
+      </c>
+      <c r="AR45" s="26">
+        <v>52.03295220435264</v>
+      </c>
+      <c r="AS45" s="26">
+        <v>-31.382952204352641</v>
+      </c>
+      <c r="AT45" s="26">
+        <v>-1.4845508174906041</v>
+      </c>
     </row>
-    <row r="46" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="7:46" x14ac:dyDescent="0.25">
       <c r="G46" s="22">
         <v>0</v>
       </c>
@@ -12154,8 +14641,53 @@
       <c r="J46" s="25">
         <v>0</v>
       </c>
+      <c r="L46" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="M46" s="26">
+        <v>1000.701724137929</v>
+      </c>
+      <c r="N46" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="O46" s="26">
+        <v>5575432.8303571409</v>
+      </c>
+      <c r="AD46" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="AE46" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="AF46" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="AG46" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="AH46" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="AI46" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="AJ46" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="AQ46" s="26">
+        <v>18</v>
+      </c>
+      <c r="AR46" s="26">
+        <v>115.41297282637107</v>
+      </c>
+      <c r="AS46" s="26">
+        <v>-8.7129728263710717</v>
+      </c>
+      <c r="AT46" s="26">
+        <v>-0.41216170001905056</v>
+      </c>
     </row>
-    <row r="47" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="7:46" x14ac:dyDescent="0.25">
       <c r="G47" s="22">
         <v>-7</v>
       </c>
@@ -12168,8 +14700,53 @@
       <c r="J47" s="25">
         <v>-7</v>
       </c>
+      <c r="L47" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="M47" s="26">
+        <v>-1.4332486796402131</v>
+      </c>
+      <c r="N47" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="O47" s="26">
+        <v>7.7361174501715091E-2</v>
+      </c>
+      <c r="AD47" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE47" s="26">
+        <v>71019042.932112128</v>
+      </c>
+      <c r="AF47" s="26">
+        <v>1</v>
+      </c>
+      <c r="AG47" s="26">
+        <v>71019042.932112128</v>
+      </c>
+      <c r="AH47" s="26">
+        <v>25.471134022682723</v>
+      </c>
+      <c r="AI47" s="26">
+        <v>5.0625423648206887E-6</v>
+      </c>
+      <c r="AJ47" s="26">
+        <v>4.0129733776501437</v>
+      </c>
+      <c r="AQ47" s="26">
+        <v>19</v>
+      </c>
+      <c r="AR47" s="26">
+        <v>47.103516857749973</v>
+      </c>
+      <c r="AS47" s="26">
+        <v>8.0964831422500296</v>
+      </c>
+      <c r="AT47" s="26">
+        <v>0.38299904321809214</v>
+      </c>
     </row>
-    <row r="48" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="7:46" x14ac:dyDescent="0.25">
       <c r="G48" s="22">
         <v>41</v>
       </c>
@@ -12182,8 +14759,47 @@
       <c r="J48" s="25">
         <v>41</v>
       </c>
+      <c r="L48" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="M48" s="26">
+        <v>6.1149176807873219E-2</v>
+      </c>
+      <c r="N48" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="O48" s="26">
+        <v>1.0301417506403849</v>
+      </c>
+      <c r="AD48" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="AE48" s="26">
+        <v>156140138.89827582</v>
+      </c>
+      <c r="AF48" s="26">
+        <v>56</v>
+      </c>
+      <c r="AG48" s="26">
+        <v>2788216.7660406395</v>
+      </c>
+      <c r="AH48" s="26"/>
+      <c r="AI48" s="26"/>
+      <c r="AJ48" s="26"/>
+      <c r="AQ48" s="26">
+        <v>20</v>
+      </c>
+      <c r="AR48" s="26">
+        <v>60.404321430755601</v>
+      </c>
+      <c r="AS48" s="26">
+        <v>29.645678569244396</v>
+      </c>
+      <c r="AT48" s="26">
+        <v>1.4023701807419966</v>
+      </c>
     </row>
-    <row r="49" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="7:46" x14ac:dyDescent="0.25">
       <c r="G49" s="22">
         <v>-67</v>
       </c>
@@ -12196,8 +14812,39 @@
       <c r="J49" s="25">
         <v>-67</v>
       </c>
+      <c r="L49" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="M49" s="26">
+        <v>94.3</v>
+      </c>
+      <c r="N49" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="O49" s="26">
+        <v>7875</v>
+      </c>
+      <c r="AD49" s="26"/>
+      <c r="AE49" s="26"/>
+      <c r="AF49" s="26"/>
+      <c r="AG49" s="26"/>
+      <c r="AH49" s="26"/>
+      <c r="AI49" s="26"/>
+      <c r="AJ49" s="26"/>
+      <c r="AQ49" s="26">
+        <v>21</v>
+      </c>
+      <c r="AR49" s="26">
+        <v>42.232883914190083</v>
+      </c>
+      <c r="AS49" s="26">
+        <v>-2.5828839141900843</v>
+      </c>
+      <c r="AT49" s="26">
+        <v>-0.12218169920172163</v>
+      </c>
     </row>
-    <row r="50" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="7:46" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G50" s="22">
         <v>52</v>
       </c>
@@ -12210,8 +14857,45 @@
       <c r="J50" s="25">
         <v>52</v>
       </c>
+      <c r="L50" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="M50" s="26">
+        <v>18.95</v>
+      </c>
+      <c r="N50" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="O50" s="26">
+        <v>20.149999999999999</v>
+      </c>
+      <c r="AD50" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="AE50" s="27">
+        <v>227159181.83038795</v>
+      </c>
+      <c r="AF50" s="27">
+        <v>57</v>
+      </c>
+      <c r="AG50" s="27"/>
+      <c r="AH50" s="27"/>
+      <c r="AI50" s="27"/>
+      <c r="AJ50" s="27"/>
+      <c r="AQ50" s="26">
+        <v>22</v>
+      </c>
+      <c r="AR50" s="26">
+        <v>43.853438276012959</v>
+      </c>
+      <c r="AS50" s="26">
+        <v>-24.053438276012958</v>
+      </c>
+      <c r="AT50" s="26">
+        <v>-1.1378327705945475</v>
+      </c>
     </row>
-    <row r="51" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="7:46" x14ac:dyDescent="0.25">
       <c r="G51" s="22">
         <v>-56</v>
       </c>
@@ -12224,8 +14908,33 @@
       <c r="J51" s="25">
         <v>-56</v>
       </c>
+      <c r="L51" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="M51" s="26">
+        <v>113.25</v>
+      </c>
+      <c r="N51" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="O51" s="26">
+        <v>7895.15</v>
+      </c>
+      <c r="R51" s="9"/>
+      <c r="AQ51" s="26">
+        <v>23</v>
+      </c>
+      <c r="AR51" s="26">
+        <v>42.038536988879223</v>
+      </c>
+      <c r="AS51" s="26">
+        <v>-21.888536988879224</v>
+      </c>
+      <c r="AT51" s="26">
+        <v>-1.0354234766991472</v>
+      </c>
     </row>
-    <row r="52" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="7:46" x14ac:dyDescent="0.25">
       <c r="G52" s="22">
         <v>-20</v>
       </c>
@@ -12238,8 +14947,33 @@
       <c r="J52" s="25">
         <v>-20</v>
       </c>
+      <c r="L52" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="M52" s="26">
+        <v>1871.6000000000004</v>
+      </c>
+      <c r="N52" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="O52" s="26">
+        <v>66051.850000000006</v>
+      </c>
+      <c r="R52" s="9"/>
+      <c r="AQ52" s="26">
+        <v>24</v>
+      </c>
+      <c r="AR52" s="26">
+        <v>76.771322494627199</v>
+      </c>
+      <c r="AS52" s="26">
+        <v>-16.871322494627201</v>
+      </c>
+      <c r="AT52" s="26">
+        <v>-0.79808730034240194</v>
+      </c>
     </row>
-    <row r="53" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="7:46" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G53" s="22">
         <v>-22</v>
       </c>
@@ -12252,6 +14986,113 @@
       <c r="J53" s="25">
         <v>-22</v>
       </c>
+      <c r="L53" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="M53" s="27">
+        <v>29</v>
+      </c>
+      <c r="N53" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="O53" s="27">
+        <v>29</v>
+      </c>
+      <c r="R53" s="9"/>
+      <c r="AQ53" s="26">
+        <v>25</v>
+      </c>
+      <c r="AR53" s="26">
+        <v>71.441233486614465</v>
+      </c>
+      <c r="AS53" s="26">
+        <v>-11.841233486614463</v>
+      </c>
+      <c r="AT53" s="26">
+        <v>-0.56014210320890467</v>
+      </c>
+    </row>
+    <row r="54" spans="7:46" x14ac:dyDescent="0.25">
+      <c r="R54" s="9"/>
+      <c r="AQ54" s="26">
+        <v>26</v>
+      </c>
+      <c r="AR54" s="26">
+        <v>57.092450493278719</v>
+      </c>
+      <c r="AS54" s="26">
+        <v>-1.7924504932787215</v>
+      </c>
+      <c r="AT54" s="26">
+        <v>-8.4790743323991655E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="7:46" x14ac:dyDescent="0.25">
+      <c r="R55" s="9"/>
+      <c r="AQ55" s="26">
+        <v>27</v>
+      </c>
+      <c r="AR55" s="26">
+        <v>89.170158004010631</v>
+      </c>
+      <c r="AS55" s="26">
+        <v>10.179841995989364</v>
+      </c>
+      <c r="AT55" s="26">
+        <v>0.48155102358328084</v>
+      </c>
+    </row>
+    <row r="56" spans="7:46" x14ac:dyDescent="0.25">
+      <c r="R56" s="9"/>
+      <c r="AQ56" s="26">
+        <v>28</v>
+      </c>
+      <c r="AR56" s="26">
+        <v>42.138700404231741</v>
+      </c>
+      <c r="AS56" s="26">
+        <v>-11.938700404231742</v>
+      </c>
+      <c r="AT56" s="26">
+        <v>-0.56475271445047392</v>
+      </c>
+    </row>
+    <row r="57" spans="7:46" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R57" s="9"/>
+      <c r="AQ57" s="27">
+        <v>29</v>
+      </c>
+      <c r="AR57" s="27">
+        <v>105.31889252099465</v>
+      </c>
+      <c r="AS57" s="27">
+        <v>-15.068892520994652</v>
+      </c>
+      <c r="AT57" s="27">
+        <v>-0.71282448397630327</v>
+      </c>
+    </row>
+    <row r="58" spans="7:46" x14ac:dyDescent="0.25">
+      <c r="R58" s="9"/>
+    </row>
+    <row r="59" spans="7:46" x14ac:dyDescent="0.25">
+      <c r="R59" s="9"/>
+    </row>
+    <row r="60" spans="7:46" x14ac:dyDescent="0.25">
+      <c r="R60" s="9"/>
+    </row>
+    <row r="61" spans="7:46" x14ac:dyDescent="0.25">
+      <c r="R61" s="9"/>
+    </row>
+    <row r="62" spans="7:46" x14ac:dyDescent="0.25">
+      <c r="R62" s="9"/>
+    </row>
+    <row r="63" spans="7:46" x14ac:dyDescent="0.25">
+      <c r="R63" s="9"/>
+    </row>
+    <row r="64" spans="7:46" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R64" s="30"/>
+      <c r="S64" s="30"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B30">
